--- a/Другое/работа/1. Отчет о проделанной работе/1. Собянин.xlsx
+++ b/Другое/работа/1. Отчет о проделанной работе/1. Собянин.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="июль" sheetId="10" r:id="rId1"/>
     <sheet name="август" sheetId="11" r:id="rId2"/>
     <sheet name="сентябрь" sheetId="12" r:id="rId3"/>
     <sheet name="3-ий квартал" sheetId="13" r:id="rId4"/>
+    <sheet name="за 9 месяцев" sheetId="14" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3-ий квартал'!$E$1:$I$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">август!$E$1:$I$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'за 9 месяцев'!$E$1:$I$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">июль!$E$1:$I$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">сентябрь!$E$1:$I$70</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="55">
   <si>
     <t>№</t>
   </si>
@@ -394,29 +396,126 @@
     <t>Написание письма в министерство транспорта</t>
   </si>
   <si>
+    <t>Отчет о проделанной работе (ежеквартальный)</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Итог периода: </t>
+      <t xml:space="preserve">Разработка системы сбора данных для внедрения системы ключевых показателей оценки труда </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>производительность труда — 107,25%</t>
+      <t>(KPI)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Разработка ведомости расценок для установки и разборки металлического дорожного </t>
     </r>
     <r>
       <rPr>
-        <sz val="14"/>
+        <b/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve"> при полном соблюдении требований к качеству. Что стоит за этим результатом? Дисциплина как база, четкое планирование как инструмент и отсутствие «слепых зон», где обычно теряется время. Такой подход позволяет стабильно закрывать KPI на уровне выше ожидаемого.</t>
+      <t>барьерного ограждения</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Проверка и </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>составление локальных смет</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> на отдельные работы по содержанию а/д</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Пересчет стоимости рабочей документации по объекту "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ТПУ Завидово 1 этап"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Приемка работ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> по ремонту (в части расценок)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Приемка работ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> по содержанию (в части расценок)</t>
     </r>
   </si>
   <si>
@@ -432,7 +531,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>производительность труда — 107,25%</t>
+      <t>производительность труда — 111,00%</t>
     </r>
     <r>
       <rPr>
@@ -445,15 +544,50 @@
       <t xml:space="preserve"> при полном соблюдении требований к качеству. Такой результат — не случайность, а следствие системы. В ее основе — дисциплина и четкое планирование, которое я веду ежедневно. Таск-трекеры и продуманные чек-листы позволяют мне не просто фиксировать задачи, а управлять временем и ресурсами. Планирование — это мой главный рабочий инструмент, который дает стабильность и позволяет закрывать KPI выше ожидаемого уровня.</t>
     </r>
   </si>
+  <si>
+    <t>Проверка и корректиовка изменений, вносимых в сметы контрактов и ведомости объемов и стоимости работ при укрупнении и разукрупнении позиций, исключении и замене ресурсов</t>
+  </si>
+  <si>
+    <t>Сбора информации для внесения изменений в 403-па</t>
+  </si>
+  <si>
+    <t>Участие в производственных совещания, планерках и обучающих курсах</t>
+  </si>
+  <si>
+    <r>
+      <t>За период достигнута</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> производительность 200,83%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> при соблюдении всех требований к качеству. Драйверами результата стали трудовая дисциплина, системное планирование и высокая самоотдача. Продуманная организация процессов исключает потери времени, что обеспечивает стабильное перевыполнение KPI.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,7 +705,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -966,11 +1100,115 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1115,12 +1353,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1136,29 +1395,59 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,6 +1455,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1212,7 +1509,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1244,9 +1541,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1278,6 +1576,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1453,9 +1752,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:O70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="2"/>
     <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
@@ -1467,19 +1766,19 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1">
-      <c r="E1" s="59" t="s">
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="19">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1">
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
@@ -1490,7 +1789,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1">
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="18" t="s">
         <v>7</v>
       </c>
@@ -1501,7 +1800,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="5:10" ht="35.25" customHeight="1">
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
@@ -1513,14 +1812,14 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="5:10" ht="16.5" thickBot="1">
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1">
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="31" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="5:10" ht="162" customHeight="1">
+    <row r="7" spans="5:10" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="35">
         <v>1</v>
       </c>
@@ -1555,7 +1854,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="8" spans="5:10" ht="86.25" customHeight="1">
+    <row r="8" spans="5:10" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="35">
         <v>2</v>
       </c>
@@ -1573,7 +1872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="5:10" ht="18.75">
+    <row r="9" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E9" s="35">
         <v>3</v>
       </c>
@@ -1591,7 +1890,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="5:10" ht="18.75">
+    <row r="10" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E10" s="35">
         <v>4</v>
       </c>
@@ -1609,7 +1908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="5:10" ht="18.75">
+    <row r="11" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E11" s="35">
         <v>5</v>
       </c>
@@ -1627,7 +1926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="5:10" ht="31.5">
+    <row r="12" spans="5:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="E12" s="37">
         <v>6</v>
       </c>
@@ -1645,7 +1944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="5:10" ht="32.25" thickBot="1">
+    <row r="13" spans="5:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E13" s="38">
         <v>7</v>
       </c>
@@ -1663,7 +1962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="5:10" ht="18.75" hidden="1">
+    <row r="14" spans="5:10" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="E14" s="27">
         <v>8</v>
       </c>
@@ -1675,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="5:10" ht="18.75" hidden="1">
+    <row r="15" spans="5:10" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="E15" s="5">
         <v>9</v>
       </c>
@@ -1687,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="5:10" ht="20.25" hidden="1">
+    <row r="16" spans="5:10" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E16" s="5">
         <v>10</v>
       </c>
@@ -1699,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:9" ht="20.25" hidden="1">
+    <row r="17" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E17" s="5">
         <v>11</v>
       </c>
@@ -1711,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="5:9" ht="20.25" hidden="1">
+    <row r="18" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E18" s="7">
         <v>12</v>
       </c>
@@ -1723,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="5:9" ht="20.25" hidden="1">
+    <row r="19" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E19" s="5">
         <v>13</v>
       </c>
@@ -1735,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:9" ht="20.25" hidden="1">
+    <row r="20" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E20" s="5">
         <v>14</v>
       </c>
@@ -1747,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:9" ht="20.25" hidden="1">
+    <row r="21" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E21" s="5">
         <v>15</v>
       </c>
@@ -1759,7 +2058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="5:9" ht="20.25" hidden="1">
+    <row r="22" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E22" s="5">
         <v>16</v>
       </c>
@@ -1771,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:9" ht="20.25" hidden="1">
+    <row r="23" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E23" s="5">
         <v>17</v>
       </c>
@@ -1783,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1">
+    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E24" s="7">
         <v>18</v>
       </c>
@@ -1795,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1">
+    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E25" s="5">
         <v>19</v>
       </c>
@@ -1807,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1">
+    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E26" s="5">
         <v>20</v>
       </c>
@@ -1819,7 +2118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1">
+    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E27" s="13">
         <v>21</v>
       </c>
@@ -1831,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1">
+    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E28" s="5">
         <v>22</v>
       </c>
@@ -1843,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1">
+    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E29" s="5">
         <v>23</v>
       </c>
@@ -1855,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1">
+    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E30" s="5">
         <v>24</v>
       </c>
@@ -1867,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1">
+    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E31" s="7">
         <v>25</v>
       </c>
@@ -1879,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1">
+    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E32" s="5">
         <v>26</v>
       </c>
@@ -1891,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1">
+    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E33" s="5">
         <v>27</v>
       </c>
@@ -1903,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1">
+    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E34" s="5">
         <v>28</v>
       </c>
@@ -1915,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1">
+    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E35" s="5">
         <v>29</v>
       </c>
@@ -1927,7 +2226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1">
+    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E36" s="5">
         <v>30</v>
       </c>
@@ -1939,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1">
+    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E37" s="5">
         <v>31</v>
       </c>
@@ -1951,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1">
+    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E38" s="7">
         <v>32</v>
       </c>
@@ -1963,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1">
+    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E39" s="5">
         <v>33</v>
       </c>
@@ -1975,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1">
+    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E40" s="5">
         <v>34</v>
       </c>
@@ -1987,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1">
+    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E41" s="5">
         <v>35</v>
       </c>
@@ -1999,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1">
+    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="5">
         <v>36</v>
       </c>
@@ -2011,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1">
+    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E43" s="5">
         <v>37</v>
       </c>
@@ -2023,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1">
+    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E44" s="5">
         <v>38</v>
       </c>
@@ -2035,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1">
+    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E45" s="7">
         <v>39</v>
       </c>
@@ -2047,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1">
+    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E46" s="5">
         <v>40</v>
       </c>
@@ -2059,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1">
+    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E47" s="5">
         <v>41</v>
       </c>
@@ -2071,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1">
+    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E48" s="5">
         <v>42</v>
       </c>
@@ -2083,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1">
+    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E49" s="5">
         <v>43</v>
       </c>
@@ -2095,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1">
+    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E50" s="5">
         <v>44</v>
       </c>
@@ -2107,7 +2406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1">
+    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E51" s="5">
         <v>45</v>
       </c>
@@ -2119,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1">
+    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E52" s="7">
         <v>46</v>
       </c>
@@ -2131,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1">
+    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E53" s="5">
         <v>47</v>
       </c>
@@ -2143,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1">
+    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E54" s="5">
         <v>48</v>
       </c>
@@ -2155,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1">
+    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E55" s="5">
         <v>49</v>
       </c>
@@ -2167,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1">
+    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E56" s="5">
         <v>50</v>
       </c>
@@ -2179,155 +2478,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:9">
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="5:9" ht="15.75" thickBot="1">
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="5:9" ht="18.75">
-      <c r="E59" s="60" t="s">
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="5:9" ht="18.75">
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="64"/>
+      <c r="G60" s="60"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="5:9" ht="18.75">
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="53"/>
+      <c r="G61" s="54"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>23</v>
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="5:9" ht="18.75">
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="53"/>
+      <c r="G62" s="54"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>184</v>
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="5:9" ht="18.75">
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="53"/>
+      <c r="G63" s="54"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>80</v>
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="5:9" ht="47.25" customHeight="1">
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="53"/>
+      <c r="G64" s="54"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>148.5</v>
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="5:15" ht="18.75">
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="53"/>
+      <c r="G65" s="54"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>6.46</v>
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="5:15" ht="19.5" thickBot="1">
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="58"/>
+      <c r="G66" s="65"/>
       <c r="H66" s="26">
         <f>H65/6</f>
         <v>1.0766666666666667</v>
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="5:15" ht="34.5" customHeight="1">
-      <c r="E67" s="54" t="s">
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="54"/>
+      <c r="F67" s="61"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="5:15" ht="81" customHeight="1">
-      <c r="E68" s="55" t="s">
+    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-    </row>
-    <row r="69" spans="5:15" ht="39" customHeight="1">
-      <c r="E69" s="56" t="s">
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="63"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="5:15">
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -2336,18 +2635,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="F66:G66"/>
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="E59:H59"/>
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="F66:G66"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -2358,9 +2657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:O70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="2"/>
     <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
@@ -2372,19 +2671,19 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1">
-      <c r="E1" s="59" t="s">
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1">
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
@@ -2395,7 +2694,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1">
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="18" t="s">
         <v>7</v>
       </c>
@@ -2406,7 +2705,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="5:10" ht="35.25" customHeight="1">
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
@@ -2418,14 +2717,14 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="5:10" ht="16.5" thickBot="1">
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1">
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="31" t="s">
         <v>0</v>
       </c>
@@ -2442,7 +2741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="5:10" ht="117.75" customHeight="1">
+    <row r="7" spans="5:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="35">
         <v>1</v>
       </c>
@@ -2461,7 +2760,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="8" spans="5:10" ht="78" customHeight="1">
+    <row r="8" spans="5:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="35">
         <v>2</v>
       </c>
@@ -2480,7 +2779,7 @@
         <v>40.25</v>
       </c>
     </row>
-    <row r="9" spans="5:10" ht="62.25" customHeight="1">
+    <row r="9" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="42">
         <v>5</v>
       </c>
@@ -2498,7 +2797,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="5:10" ht="62.25" customHeight="1">
+    <row r="10" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="42">
         <v>6</v>
       </c>
@@ -2516,7 +2815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="5:10" ht="62.25" customHeight="1">
+    <row r="11" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="42">
         <v>7</v>
       </c>
@@ -2534,7 +2833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="5:10" ht="62.25" customHeight="1">
+    <row r="12" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="42">
         <v>8</v>
       </c>
@@ -2552,7 +2851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="5:10" ht="38.25" customHeight="1">
+    <row r="13" spans="5:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="48">
         <v>9</v>
       </c>
@@ -2570,7 +2869,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="14" spans="5:10" ht="146.25" customHeight="1">
+    <row r="14" spans="5:10" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" s="48">
         <v>10</v>
       </c>
@@ -2588,7 +2887,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="15" spans="5:10" ht="79.5" thickBot="1">
+    <row r="15" spans="5:10" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E15" s="49">
         <v>11</v>
       </c>
@@ -2606,7 +2905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="5:10" ht="20.25" hidden="1">
+    <row r="16" spans="5:10" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E16" s="27">
         <v>10</v>
       </c>
@@ -2618,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:9" ht="20.25" hidden="1">
+    <row r="17" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E17" s="5">
         <v>11</v>
       </c>
@@ -2630,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="5:9" ht="20.25" hidden="1">
+    <row r="18" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E18" s="7">
         <v>12</v>
       </c>
@@ -2642,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="5:9" ht="20.25" hidden="1">
+    <row r="19" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E19" s="5">
         <v>13</v>
       </c>
@@ -2654,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:9" ht="20.25" hidden="1">
+    <row r="20" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E20" s="5">
         <v>14</v>
       </c>
@@ -2666,7 +2965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:9" ht="20.25" hidden="1">
+    <row r="21" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E21" s="5">
         <v>15</v>
       </c>
@@ -2678,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="5:9" ht="20.25" hidden="1">
+    <row r="22" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E22" s="5">
         <v>16</v>
       </c>
@@ -2690,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:9" ht="20.25" hidden="1">
+    <row r="23" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E23" s="5">
         <v>17</v>
       </c>
@@ -2702,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1">
+    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E24" s="7">
         <v>18</v>
       </c>
@@ -2714,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1">
+    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E25" s="5">
         <v>19</v>
       </c>
@@ -2726,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1">
+    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E26" s="5">
         <v>20</v>
       </c>
@@ -2738,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1">
+    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E27" s="13">
         <v>21</v>
       </c>
@@ -2750,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1">
+    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E28" s="5">
         <v>22</v>
       </c>
@@ -2762,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1">
+    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E29" s="5">
         <v>23</v>
       </c>
@@ -2774,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1">
+    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E30" s="5">
         <v>24</v>
       </c>
@@ -2786,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1">
+    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E31" s="7">
         <v>25</v>
       </c>
@@ -2798,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1">
+    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E32" s="5">
         <v>26</v>
       </c>
@@ -2810,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1">
+    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E33" s="5">
         <v>27</v>
       </c>
@@ -2822,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1">
+    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E34" s="5">
         <v>28</v>
       </c>
@@ -2834,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1">
+    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E35" s="5">
         <v>29</v>
       </c>
@@ -2846,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1">
+    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E36" s="5">
         <v>30</v>
       </c>
@@ -2858,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1">
+    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E37" s="5">
         <v>31</v>
       </c>
@@ -2870,7 +3169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1">
+    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E38" s="7">
         <v>32</v>
       </c>
@@ -2882,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1">
+    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E39" s="5">
         <v>33</v>
       </c>
@@ -2894,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1">
+    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E40" s="5">
         <v>34</v>
       </c>
@@ -2906,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1">
+    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E41" s="5">
         <v>35</v>
       </c>
@@ -2918,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1">
+    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="5">
         <v>36</v>
       </c>
@@ -2930,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1">
+    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E43" s="5">
         <v>37</v>
       </c>
@@ -2942,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1">
+    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E44" s="5">
         <v>38</v>
       </c>
@@ -2954,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1">
+    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E45" s="7">
         <v>39</v>
       </c>
@@ -2966,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1">
+    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E46" s="5">
         <v>40</v>
       </c>
@@ -2978,7 +3277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1">
+    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E47" s="5">
         <v>41</v>
       </c>
@@ -2990,7 +3289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1">
+    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E48" s="5">
         <v>42</v>
       </c>
@@ -3002,7 +3301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1">
+    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E49" s="5">
         <v>43</v>
       </c>
@@ -3014,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1">
+    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E50" s="5">
         <v>44</v>
       </c>
@@ -3026,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1">
+    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E51" s="5">
         <v>45</v>
       </c>
@@ -3038,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1">
+    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E52" s="7">
         <v>46</v>
       </c>
@@ -3050,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1">
+    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E53" s="5">
         <v>47</v>
       </c>
@@ -3062,7 +3361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1">
+    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E54" s="5">
         <v>48</v>
       </c>
@@ -3074,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1">
+    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E55" s="5">
         <v>49</v>
       </c>
@@ -3086,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1">
+    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E56" s="5">
         <v>50</v>
       </c>
@@ -3098,155 +3397,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:9">
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="5:9" ht="15.75" thickBot="1">
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="5:9" ht="18.75">
-      <c r="E59" s="60" t="s">
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="5:9" ht="18.75">
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="64"/>
+      <c r="G60" s="60"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="5:9" ht="18.75">
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="53"/>
+      <c r="G61" s="54"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>20</v>
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="5:9" ht="18.75">
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="53"/>
+      <c r="G62" s="54"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>160</v>
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="5:9" ht="18.75">
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="53"/>
+      <c r="G63" s="54"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>99</v>
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="5:9" ht="47.25" customHeight="1">
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="53"/>
+      <c r="G64" s="54"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>145.1</v>
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="5:15" ht="18.75">
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="53"/>
+      <c r="G65" s="54"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>7.26</v>
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="5:15" ht="19.5" thickBot="1">
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="58"/>
+      <c r="G66" s="65"/>
       <c r="H66" s="26">
         <f>H65/6</f>
         <v>1.21</v>
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="5:15" ht="34.5" customHeight="1">
-      <c r="E67" s="54" t="s">
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="54"/>
+      <c r="F67" s="61"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="5:15" ht="81" customHeight="1">
-      <c r="E68" s="55" t="s">
+    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-    </row>
-    <row r="69" spans="5:15" ht="39" customHeight="1">
-      <c r="E69" s="56" t="s">
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="63"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="5:15">
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -3277,9 +3576,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:O70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="2"/>
     <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
@@ -3291,19 +3590,19 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1">
-      <c r="E1" s="59" t="s">
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1">
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
@@ -3314,7 +3613,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1">
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="18" t="s">
         <v>7</v>
       </c>
@@ -3325,26 +3624,26 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="5:10" ht="35.25" customHeight="1">
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="65" t="str">
+      <c r="F4" s="66" t="str">
         <f>"с 01 сентября по 28 сентября (" &amp; J1 &amp; " рабочих дней)"</f>
         <v>с 01 сентября по 28 сентября (20 рабочих дней)</v>
       </c>
-      <c r="G4" s="65"/>
+      <c r="G4" s="66"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="5:10" ht="16.5" thickBot="1">
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1">
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="31" t="s">
         <v>0</v>
       </c>
@@ -3361,7 +3660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="5:10" ht="141.75" customHeight="1">
+    <row r="7" spans="5:10" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="35">
         <v>1</v>
       </c>
@@ -3369,6 +3668,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="14">
+        <f>21</f>
         <v>21</v>
       </c>
       <c r="H7" s="14">
@@ -3379,7 +3679,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="5:10" ht="78" customHeight="1">
+    <row r="8" spans="5:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="35">
         <v>2</v>
       </c>
@@ -3397,7 +3697,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="9" spans="5:10" ht="62.25" customHeight="1">
+    <row r="9" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="42">
         <v>3</v>
       </c>
@@ -3405,6 +3705,7 @@
         <v>33</v>
       </c>
       <c r="G9" s="44">
+        <f>3</f>
         <v>3</v>
       </c>
       <c r="H9" s="44">
@@ -3415,7 +3716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="5:10" ht="62.25" customHeight="1">
+    <row r="10" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="42">
         <v>4</v>
       </c>
@@ -3433,7 +3734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="5:10" ht="62.25" customHeight="1">
+    <row r="11" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="42">
         <v>5</v>
       </c>
@@ -3451,7 +3752,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="5:10" ht="62.25" customHeight="1">
+    <row r="12" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="42">
         <v>6</v>
       </c>
@@ -3462,14 +3763,14 @@
         <v>1</v>
       </c>
       <c r="H12" s="44">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I12" s="36">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="5:10" ht="38.25" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="48">
         <v>7</v>
       </c>
@@ -3487,29 +3788,29 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="14" spans="5:10" ht="38.25" customHeight="1">
-      <c r="E14" s="48">
+    <row r="14" spans="5:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="67">
         <v>8</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="69">
         <v>3</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="69">
         <v>16</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="70">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="5:10" ht="38.25" customHeight="1" thickBot="1">
+    <row r="15" spans="5:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E15" s="49">
         <v>9</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="52" t="s">
         <v>42</v>
       </c>
       <c r="G15" s="51">
@@ -3518,36 +3819,36 @@
       <c r="H15" s="51">
         <v>4</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="73">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="5:10" ht="20.25" hidden="1">
-      <c r="E16" s="27">
+    <row r="16" spans="5:10" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="71">
         <v>10</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="46"/>
       <c r="H16" s="46"/>
-      <c r="I16" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9" ht="20.25" hidden="1">
-      <c r="E17" s="5">
+      <c r="I16" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="27">
         <v>11</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9" ht="20.25" hidden="1">
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E18" s="7">
         <v>12</v>
       </c>
@@ -3559,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="5:9" ht="20.25" hidden="1">
+    <row r="19" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E19" s="5">
         <v>13</v>
       </c>
@@ -3571,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:9" ht="20.25" hidden="1">
+    <row r="20" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E20" s="5">
         <v>14</v>
       </c>
@@ -3583,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:9" ht="20.25" hidden="1">
+    <row r="21" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E21" s="5">
         <v>15</v>
       </c>
@@ -3595,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="5:9" ht="20.25" hidden="1">
+    <row r="22" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E22" s="5">
         <v>16</v>
       </c>
@@ -3607,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:9" ht="20.25" hidden="1">
+    <row r="23" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E23" s="5">
         <v>17</v>
       </c>
@@ -3619,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1">
+    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E24" s="7">
         <v>18</v>
       </c>
@@ -3631,7 +3932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1">
+    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E25" s="5">
         <v>19</v>
       </c>
@@ -3643,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1">
+    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E26" s="5">
         <v>20</v>
       </c>
@@ -3655,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1">
+    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E27" s="13">
         <v>21</v>
       </c>
@@ -3667,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1">
+    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E28" s="5">
         <v>22</v>
       </c>
@@ -3679,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1">
+    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E29" s="5">
         <v>23</v>
       </c>
@@ -3691,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1">
+    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E30" s="5">
         <v>24</v>
       </c>
@@ -3703,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1">
+    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E31" s="7">
         <v>25</v>
       </c>
@@ -3715,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1">
+    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E32" s="5">
         <v>26</v>
       </c>
@@ -3727,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1">
+    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E33" s="5">
         <v>27</v>
       </c>
@@ -3739,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1">
+    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E34" s="5">
         <v>28</v>
       </c>
@@ -3751,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1">
+    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E35" s="5">
         <v>29</v>
       </c>
@@ -3763,7 +4064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1">
+    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E36" s="5">
         <v>30</v>
       </c>
@@ -3775,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1">
+    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E37" s="5">
         <v>31</v>
       </c>
@@ -3787,7 +4088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1">
+    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E38" s="7">
         <v>32</v>
       </c>
@@ -3799,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1">
+    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E39" s="5">
         <v>33</v>
       </c>
@@ -3811,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1">
+    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E40" s="5">
         <v>34</v>
       </c>
@@ -3823,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1">
+    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E41" s="5">
         <v>35</v>
       </c>
@@ -3835,7 +4136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1">
+    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="5">
         <v>36</v>
       </c>
@@ -3847,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1">
+    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E43" s="5">
         <v>37</v>
       </c>
@@ -3859,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1">
+    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E44" s="5">
         <v>38</v>
       </c>
@@ -3871,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1">
+    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E45" s="7">
         <v>39</v>
       </c>
@@ -3883,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1">
+    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E46" s="5">
         <v>40</v>
       </c>
@@ -3895,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1">
+    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E47" s="5">
         <v>41</v>
       </c>
@@ -3907,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1">
+    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E48" s="5">
         <v>42</v>
       </c>
@@ -3919,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1">
+    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E49" s="5">
         <v>43</v>
       </c>
@@ -3931,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1">
+    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E50" s="5">
         <v>44</v>
       </c>
@@ -3943,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1">
+    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E51" s="5">
         <v>45</v>
       </c>
@@ -3955,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1">
+    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E52" s="7">
         <v>46</v>
       </c>
@@ -3967,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1">
+    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E53" s="5">
         <v>47</v>
       </c>
@@ -3979,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1">
+    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E54" s="5">
         <v>48</v>
       </c>
@@ -3991,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1">
+    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E55" s="5">
         <v>49</v>
       </c>
@@ -4003,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1">
+    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E56" s="5">
         <v>50</v>
       </c>
@@ -4015,155 +4316,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:9">
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="5:9" ht="15.75" thickBot="1">
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="5:9" ht="18.75">
-      <c r="E59" s="60" t="s">
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="5:9" ht="18.75">
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="64"/>
+      <c r="G60" s="60"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="5:9" ht="18.75">
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="53"/>
+      <c r="G61" s="54"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>20</v>
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="5:9" ht="18.75">
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="53"/>
+      <c r="G62" s="54"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>160</v>
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="5:9" ht="18.75">
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="53"/>
+      <c r="G63" s="54"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>60</v>
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="5:9" ht="47.25" customHeight="1">
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="53"/>
+      <c r="G64" s="54"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
-        <v>171.55</v>
+        <v>177.55</v>
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="5:15" ht="18.75">
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="53"/>
+      <c r="G65" s="54"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
-        <v>8.58</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="5:15" ht="19.5" thickBot="1">
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="58"/>
+      <c r="G66" s="65"/>
       <c r="H66" s="26">
         <f>H65/8</f>
-        <v>1.0725</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="5:15" ht="34.5" customHeight="1">
-      <c r="E67" s="54" t="s">
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="54"/>
+      <c r="F67" s="61"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="5:15" ht="81" customHeight="1">
-      <c r="E68" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-    </row>
-    <row r="69" spans="5:15" ht="39" customHeight="1">
-      <c r="E69" s="56" t="s">
+    <row r="68" spans="5:15" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="63"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="5:15">
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -4172,11 +4473,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:I68"/>
     <mergeCell ref="E69:F69"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="E59:H59"/>
@@ -4185,6 +4481,11 @@
     <mergeCell ref="F62:G62"/>
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:I68"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -4195,9 +4496,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:O70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="2"/>
     <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
@@ -4209,19 +4510,19 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1">
-      <c r="E1" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
@@ -4232,7 +4533,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1">
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="18" t="s">
         <v>7</v>
       </c>
@@ -4243,151 +4544,155 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="5:10" ht="35.25" customHeight="1">
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="65" t="str">
-        <f>"с 01 сентября по 28 сентября (" &amp; J1 &amp; " рабочих дней)"</f>
-        <v>с 01 сентября по 28 сентября (20 рабочих дней)</v>
-      </c>
-      <c r="G4" s="65"/>
+      <c r="F4" s="66" t="str">
+        <f>"с 01 июля по 28 сентября (" &amp; J1 &amp; " рабочих дня)"</f>
+        <v>с 01 июля по 28 сентября (63 рабочих дня)</v>
+      </c>
+      <c r="G4" s="66"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="5:10" ht="16.5" thickBot="1">
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1">
-      <c r="E6" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="32" t="s">
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="78" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="5:10" ht="141.75" customHeight="1">
-      <c r="E7" s="35">
+    <row r="7" spans="5:10" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="48">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="14">
-        <v>21</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="G7" s="16">
+        <f>21+24+25</f>
+        <v>70</v>
+      </c>
+      <c r="H7" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="79">
+        <f t="shared" ref="I7:I56" si="0">G7*H7</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="5:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="48">
         <v>2</v>
       </c>
-      <c r="I7" s="36">
-        <f t="shared" ref="I7:I56" si="0">G7*H7</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="5:10" ht="78" customHeight="1">
-      <c r="E8" s="35">
+      <c r="F8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="16">
+        <f>14+23</f>
+        <v>37</v>
+      </c>
+      <c r="H8" s="16">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="14">
-        <v>14</v>
-      </c>
-      <c r="H8" s="14">
-        <v>1.75</v>
-      </c>
-      <c r="I8" s="36">
-        <f t="shared" si="0"/>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="9" spans="5:10" ht="62.25" customHeight="1">
-      <c r="E9" s="42">
+      <c r="I8" s="79">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="48">
         <v>3</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="44">
-        <v>3</v>
-      </c>
-      <c r="H9" s="44">
+      <c r="G9" s="16">
+        <f>3+10+10</f>
+        <v>23</v>
+      </c>
+      <c r="H9" s="16">
+        <v>2</v>
+      </c>
+      <c r="I9" s="79">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="48">
+        <v>4</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="16">
         <v>1</v>
       </c>
-      <c r="I9" s="36">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="5:10" ht="62.25" customHeight="1">
-      <c r="E10" s="42">
-        <v>4</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="44">
+      <c r="H10" s="16">
+        <v>20</v>
+      </c>
+      <c r="I10" s="79">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="48">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="16">
+        <f>3+12+10</f>
+        <v>25</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="79">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="48">
+        <v>6</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="16">
         <v>1</v>
       </c>
-      <c r="H10" s="44">
-        <v>20</v>
-      </c>
-      <c r="I10" s="36">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="5:10" ht="62.25" customHeight="1">
-      <c r="E11" s="42">
-        <v>5</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="44">
-        <v>3</v>
-      </c>
-      <c r="H11" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="36">
-        <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="5:10" ht="62.25" customHeight="1">
-      <c r="E12" s="42">
-        <v>6</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="44">
-        <v>1</v>
-      </c>
-      <c r="H12" s="44">
-        <v>24</v>
-      </c>
-      <c r="I12" s="36">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="5:10" ht="38.25" customHeight="1">
+      <c r="H12" s="16">
+        <v>30</v>
+      </c>
+      <c r="I12" s="79">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="48">
         <v>7</v>
       </c>
@@ -4395,161 +4700,213 @@
         <v>31</v>
       </c>
       <c r="G13" s="16">
-        <v>13</v>
+        <f>13+21</f>
+        <v>34</v>
       </c>
       <c r="H13" s="16">
         <v>0.35</v>
       </c>
-      <c r="I13" s="36">
-        <f t="shared" si="0"/>
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="14" spans="5:10" ht="38.25" customHeight="1">
+      <c r="I13" s="79">
+        <f t="shared" si="0"/>
+        <v>11.899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" s="48">
         <v>8</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G14" s="16">
         <v>3</v>
       </c>
       <c r="H14" s="16">
+        <v>20</v>
+      </c>
+      <c r="I14" s="79">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="48">
+        <v>9</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16">
+        <v>4</v>
+      </c>
+      <c r="I15" s="79">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="48">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16">
+        <v>12</v>
+      </c>
+      <c r="I16" s="79">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="48">
+        <v>8</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="16">
+        <v>15</v>
+      </c>
+      <c r="H17" s="16">
+        <v>1</v>
+      </c>
+      <c r="I17" s="79">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="80">
+        <v>12</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="16">
+        <f>3+9</f>
+        <v>12</v>
+      </c>
+      <c r="H18" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I18" s="79">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="48">
+        <v>13</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="16">
+        <f>3+9</f>
+        <v>12</v>
+      </c>
+      <c r="H19" s="16">
+        <v>1</v>
+      </c>
+      <c r="I19" s="79">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="48">
+        <v>14</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="16">
+        <v>8</v>
+      </c>
+      <c r="H20" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I20" s="79">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="E21" s="81">
+        <v>15</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="46">
+        <v>20</v>
+      </c>
+      <c r="H21" s="46">
+        <v>1</v>
+      </c>
+      <c r="I21" s="82">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="E22" s="35">
         <v>16</v>
       </c>
-      <c r="I14" s="36">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="5:10" ht="38.25" customHeight="1" thickBot="1">
-      <c r="E15" s="49">
-        <v>9</v>
-      </c>
-      <c r="F15" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="51">
+      <c r="F22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="51">
-        <v>4</v>
-      </c>
-      <c r="I15" s="41">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="5:10" ht="20.25" hidden="1">
-      <c r="E16" s="27">
-        <v>10</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9" ht="20.25" hidden="1">
-      <c r="E17" s="5">
-        <v>11</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9" ht="20.25" hidden="1">
-      <c r="E18" s="7">
-        <v>12</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="5:9" ht="20.25" hidden="1">
-      <c r="E19" s="5">
-        <v>13</v>
-      </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="5:9" ht="20.25" hidden="1">
-      <c r="E20" s="5">
-        <v>14</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="5:9" ht="20.25" hidden="1">
-      <c r="E21" s="5">
-        <v>15</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="5:9" ht="20.25" hidden="1">
-      <c r="E22" s="5">
-        <v>16</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="5:9" ht="20.25" hidden="1">
-      <c r="E23" s="5">
+      <c r="H22" s="17">
+        <v>25</v>
+      </c>
+      <c r="I22" s="36">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="38">
         <v>17</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1">
-      <c r="E24" s="7">
+      <c r="F23" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="83">
+        <f>J1/2+0.5</f>
+        <v>32</v>
+      </c>
+      <c r="H23" s="83">
+        <v>1.25</v>
+      </c>
+      <c r="I23" s="41">
+        <f>ROUND(G23*H23,2)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="74">
         <v>18</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1">
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E25" s="5">
         <v>19</v>
       </c>
@@ -4561,7 +4918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1">
+    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E26" s="5">
         <v>20</v>
       </c>
@@ -4573,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1">
+    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E27" s="13">
         <v>21</v>
       </c>
@@ -4585,7 +4942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1">
+    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E28" s="5">
         <v>22</v>
       </c>
@@ -4597,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1">
+    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E29" s="5">
         <v>23</v>
       </c>
@@ -4609,7 +4966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1">
+    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E30" s="5">
         <v>24</v>
       </c>
@@ -4621,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1">
+    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E31" s="7">
         <v>25</v>
       </c>
@@ -4633,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1">
+    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E32" s="5">
         <v>26</v>
       </c>
@@ -4645,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1">
+    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E33" s="5">
         <v>27</v>
       </c>
@@ -4657,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1">
+    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E34" s="5">
         <v>28</v>
       </c>
@@ -4669,7 +5026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1">
+    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E35" s="5">
         <v>29</v>
       </c>
@@ -4681,7 +5038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1">
+    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E36" s="5">
         <v>30</v>
       </c>
@@ -4693,7 +5050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1">
+    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E37" s="5">
         <v>31</v>
       </c>
@@ -4705,7 +5062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1">
+    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E38" s="7">
         <v>32</v>
       </c>
@@ -4717,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1">
+    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E39" s="5">
         <v>33</v>
       </c>
@@ -4729,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1">
+    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E40" s="5">
         <v>34</v>
       </c>
@@ -4741,7 +5098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1">
+    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E41" s="5">
         <v>35</v>
       </c>
@@ -4753,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1">
+    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="5">
         <v>36</v>
       </c>
@@ -4765,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1">
+    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E43" s="5">
         <v>37</v>
       </c>
@@ -4777,7 +5134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1">
+    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E44" s="5">
         <v>38</v>
       </c>
@@ -4789,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1">
+    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E45" s="7">
         <v>39</v>
       </c>
@@ -4801,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1">
+    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E46" s="5">
         <v>40</v>
       </c>
@@ -4813,7 +5170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1">
+    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E47" s="5">
         <v>41</v>
       </c>
@@ -4825,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1">
+    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E48" s="5">
         <v>42</v>
       </c>
@@ -4837,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1">
+    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E49" s="5">
         <v>43</v>
       </c>
@@ -4849,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1">
+    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E50" s="5">
         <v>44</v>
       </c>
@@ -4861,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1">
+    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E51" s="5">
         <v>45</v>
       </c>
@@ -4873,7 +5230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1">
+    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E52" s="7">
         <v>46</v>
       </c>
@@ -4885,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1">
+    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E53" s="5">
         <v>47</v>
       </c>
@@ -4897,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1">
+    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E54" s="5">
         <v>48</v>
       </c>
@@ -4909,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1">
+    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E55" s="5">
         <v>49</v>
       </c>
@@ -4921,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1">
+    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="E56" s="5">
         <v>50</v>
       </c>
@@ -4933,155 +5290,1129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:9">
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="5:9" ht="15.75" thickBot="1">
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="5:9" ht="18.75">
-      <c r="E59" s="60" t="s">
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="5:9" ht="18.75">
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="64"/>
+      <c r="G60" s="60"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="5:9" ht="18.75">
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="53"/>
+      <c r="G61" s="54"/>
       <c r="H61" s="24">
         <f>J1</f>
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="5:9" ht="18.75">
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="53"/>
+      <c r="G62" s="54"/>
       <c r="H62" s="24">
         <f>H61*8</f>
-        <v>160</v>
+        <v>504</v>
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="5:9" ht="18.75">
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="53"/>
+      <c r="G63" s="54"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
-        <v>60</v>
+        <v>296</v>
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="5:9" ht="47.25" customHeight="1">
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="53"/>
+      <c r="G64" s="54"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
-        <v>171.55</v>
+        <v>607.4</v>
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="5:15" ht="18.75">
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="53"/>
+      <c r="G65" s="54"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
-        <v>8.58</v>
+        <v>9.64</v>
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="5:15" ht="19.5" thickBot="1">
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="58"/>
+      <c r="G66" s="65"/>
       <c r="H66" s="26">
-        <f>H65/8</f>
-        <v>1.0725</v>
+        <f>H65/(8-3.2)</f>
+        <v>2.0083333333333337</v>
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="5:15" ht="34.5" customHeight="1">
-      <c r="E67" s="54" t="s">
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="54"/>
+      <c r="F67" s="61"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="5:15" ht="81" customHeight="1">
-      <c r="E68" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-    </row>
-    <row r="69" spans="5:15" ht="39" customHeight="1">
-      <c r="E69" s="56" t="s">
+    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="63"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="5:15">
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:I68"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="55" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="4" max="1048575" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E1:O70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="52.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="19">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="66" t="str">
+        <f>"с 01 июля по 28 сентября (" &amp; J1 &amp; " рабочих дня)"</f>
+        <v>с 01 июля по 28 сентября (63 рабочих дня)</v>
+      </c>
+      <c r="G4" s="66"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="5:10" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="48">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="16">
+        <f>21+24+25</f>
+        <v>70</v>
+      </c>
+      <c r="H7" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="79">
+        <f t="shared" ref="I7:I56" si="0">G7*H7</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="5:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="48">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="16">
+        <f>14+23</f>
+        <v>37</v>
+      </c>
+      <c r="H8" s="16">
+        <v>2</v>
+      </c>
+      <c r="I8" s="79">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="48">
+        <v>3</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="16">
+        <f>3+10+10</f>
+        <v>23</v>
+      </c>
+      <c r="H9" s="16">
+        <v>2</v>
+      </c>
+      <c r="I9" s="79">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="48">
+        <v>4</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="16">
+        <v>20</v>
+      </c>
+      <c r="I10" s="79">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="48">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="16">
+        <f>3+12+10</f>
+        <v>25</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="79">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="48">
+        <v>6</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="16">
+        <v>30</v>
+      </c>
+      <c r="I12" s="79">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="48">
+        <v>7</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="16">
+        <f>13+21</f>
+        <v>34</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="I13" s="79">
+        <f t="shared" si="0"/>
+        <v>11.899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="48">
+        <v>8</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="16">
+        <v>3</v>
+      </c>
+      <c r="H14" s="16">
+        <v>20</v>
+      </c>
+      <c r="I14" s="79">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="48">
+        <v>9</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16">
+        <v>4</v>
+      </c>
+      <c r="I15" s="79">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="48">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16">
+        <v>12</v>
+      </c>
+      <c r="I16" s="79">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="48">
+        <v>8</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="16">
+        <v>15</v>
+      </c>
+      <c r="H17" s="16">
+        <v>1</v>
+      </c>
+      <c r="I17" s="79">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="80">
+        <v>12</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="16">
+        <f>3+9</f>
+        <v>12</v>
+      </c>
+      <c r="H18" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I18" s="79">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="48">
+        <v>13</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="16">
+        <f>3+9</f>
+        <v>12</v>
+      </c>
+      <c r="H19" s="16">
+        <v>1</v>
+      </c>
+      <c r="I19" s="79">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="48">
+        <v>14</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="16">
+        <v>8</v>
+      </c>
+      <c r="H20" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I20" s="79">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="E21" s="81">
+        <v>15</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="46">
+        <v>20</v>
+      </c>
+      <c r="H21" s="46">
+        <v>1</v>
+      </c>
+      <c r="I21" s="82">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="E22" s="35">
+        <v>16</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="17">
+        <v>25</v>
+      </c>
+      <c r="I22" s="36">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="38">
+        <v>17</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="83">
+        <f>J1/2+0.5</f>
+        <v>32</v>
+      </c>
+      <c r="H23" s="83">
+        <v>1.25</v>
+      </c>
+      <c r="I23" s="41">
+        <f>ROUND(G23*H23,2)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="74">
+        <v>18</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="5">
+        <v>19</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="5">
+        <v>20</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="13">
+        <v>21</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="5">
+        <v>22</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="5">
+        <v>23</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="5">
+        <v>24</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="7">
+        <v>25</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="5">
+        <v>26</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="5">
+        <v>27</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E34" s="5">
+        <v>28</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="5">
+        <v>29</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="5">
+        <v>30</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="5">
+        <v>31</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="7">
+        <v>32</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="5">
+        <v>33</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="5">
+        <v>34</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="5">
+        <v>35</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="5">
+        <v>36</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="5">
+        <v>37</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="5">
+        <v>38</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="7">
+        <v>39</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="5">
+        <v>40</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="5">
+        <v>41</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="5">
+        <v>42</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="5">
+        <v>43</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="5">
+        <v>44</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="5">
+        <v>45</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="7">
+        <v>46</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="5">
+        <v>47</v>
+      </c>
+      <c r="F53" s="12"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="5">
+        <v>48</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="5">
+        <v>49</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E56" s="5">
+        <v>50</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="6"/>
+    </row>
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E60" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F60" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="60"/>
+      <c r="H60" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E61" s="23">
+        <v>1</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="54"/>
+      <c r="H61" s="24">
+        <f>J1</f>
+        <v>63</v>
+      </c>
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E62" s="23">
+        <v>2</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="54"/>
+      <c r="H62" s="24">
+        <f>H61*8</f>
+        <v>504</v>
+      </c>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E63" s="23">
+        <v>3</v>
+      </c>
+      <c r="F63" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="54"/>
+      <c r="H63" s="24">
+        <f>SUM(G7:G56)</f>
+        <v>296</v>
+      </c>
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="23">
+        <v>4</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="54"/>
+      <c r="H64" s="24">
+        <f>SUM(I7:I56)</f>
+        <v>607.4</v>
+      </c>
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E65" s="23">
+        <v>5</v>
+      </c>
+      <c r="F65" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="54"/>
+      <c r="H65" s="24">
+        <f>ROUND(H64/H61,2)</f>
+        <v>9.64</v>
+      </c>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E66" s="25">
+        <v>6</v>
+      </c>
+      <c r="F66" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="65"/>
+      <c r="H66" s="26">
+        <f>H65/(8-3.2)</f>
+        <v>2.0083333333333337</v>
+      </c>
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="61"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="63"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>

--- a/Другое/работа/1. Отчет о проделанной работе/1. Собянин.xlsx
+++ b/Другое/работа/1. Отчет о проделанной работе/1. Собянин.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010" activeTab="4"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="июль" sheetId="10" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="67">
   <si>
     <t>№</t>
   </si>
@@ -548,9 +548,6 @@
     <t>Проверка и корректиовка изменений, вносимых в сметы контрактов и ведомости объемов и стоимости работ при укрупнении и разукрупнении позиций, исключении и замене ресурсов</t>
   </si>
   <si>
-    <t>Сбора информации для внесения изменений в 403-па</t>
-  </si>
-  <si>
     <t>Участие в производственных совещания, планерках и обучающих курсах</t>
   </si>
   <si>
@@ -577,6 +574,149 @@
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> при соблюдении всех требований к качеству. Драйверами результата стали трудовая дисциплина, системное планирование и высокая самоотдача. Продуманная организация процессов исключает потери времени, что обеспечивает стабильное перевыполнение KPI.</t>
+    </r>
+  </si>
+  <si>
+    <t>Отчет о проделанной работе (за 9 месяцев)</t>
+  </si>
+  <si>
+    <t>Рассмотрение заявок участников на участие в закупках</t>
+  </si>
+  <si>
+    <t>Подведение итогов конкурентных процедур</t>
+  </si>
+  <si>
+    <t>Подготовка заявок на участие в закупке</t>
+  </si>
+  <si>
+    <t>Составление проетктов государственных контарктов</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Участие в ФАС:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>- сбор информации и подготовка доводов
+- участие в заседаниях и представление позиции</t>
+    </r>
+  </si>
+  <si>
+    <t>Сбора информации для внесения изменений 
+в 403-па</t>
+  </si>
+  <si>
+    <t>Перегистрация контрактов заключенных до 2026 года в рамках ремонта (только федеральные средства) в программе Бюджет-Смарт для корректного учета бюджетных обязательств</t>
+  </si>
+  <si>
+    <t>Составление и отправка сопроводительных писем</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Аналитическая и статистическая работа
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>- сбор информации
+    - оформление</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Публикация первого плана-графика
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>- планирование
+- доработка, исправления
+- согласование
+- публикация</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Пересчет цены контракта после экспертизы:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Бежецкая ЦРБ 1 этап
+- Строительство дороги "Подъезд к школе Радужный"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>По итогам периода</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> производительность составила 202,98%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> — при полном соблюдении стандартов качества. Такой результат стал возможен благодаря дисциплине в работе, продуманному планированию и высокой самоотдаче сотрудников. Грамотно выстроенные процессы не оставляют места для потерь времени, что позволяет стабильно перевыполнять KPI.</t>
     </r>
   </si>
 </sst>
@@ -1208,7 +1348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1356,12 +1496,78 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,73 +1586,37 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1767,13 +1937,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="19">
         <v>23</v>
       </c>
@@ -2493,22 +2663,22 @@
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="58"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="80"/>
       <c r="I59" s="6"/>
     </row>
     <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="60"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
@@ -2518,10 +2688,10 @@
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="54"/>
+      <c r="G61" s="71"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>23</v>
@@ -2532,10 +2702,10 @@
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="53" t="s">
+      <c r="F62" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="54"/>
+      <c r="G62" s="71"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>184</v>
@@ -2546,10 +2716,10 @@
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="53" t="s">
+      <c r="F63" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="54"/>
+      <c r="G63" s="71"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>80</v>
@@ -2560,10 +2730,10 @@
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="54"/>
+      <c r="G64" s="71"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>148.5</v>
@@ -2574,10 +2744,10 @@
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="54"/>
+      <c r="G65" s="71"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>6.46</v>
@@ -2588,10 +2758,10 @@
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="64" t="s">
+      <c r="F66" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="65"/>
+      <c r="G66" s="76"/>
       <c r="H66" s="26">
         <f>H65/6</f>
         <v>1.0766666666666667</v>
@@ -2599,29 +2769,29 @@
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E67" s="61" t="s">
+      <c r="E67" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="72"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
     <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="G68" s="62"/>
-      <c r="H68" s="62"/>
-      <c r="I68" s="62"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
     </row>
     <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="63" t="s">
+      <c r="E69" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="63"/>
+      <c r="F69" s="74"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -2635,18 +2805,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
     <mergeCell ref="F64:G64"/>
     <mergeCell ref="F65:G65"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="E68:I68"/>
     <mergeCell ref="E69:F69"/>
     <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -2672,13 +2842,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="19">
         <v>20</v>
       </c>
@@ -3412,22 +3582,22 @@
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="58"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="80"/>
       <c r="I59" s="6"/>
     </row>
     <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="60"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
@@ -3437,10 +3607,10 @@
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="54"/>
+      <c r="G61" s="71"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>20</v>
@@ -3451,10 +3621,10 @@
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="53" t="s">
+      <c r="F62" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="54"/>
+      <c r="G62" s="71"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>160</v>
@@ -3465,10 +3635,10 @@
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="53" t="s">
+      <c r="F63" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="54"/>
+      <c r="G63" s="71"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>99</v>
@@ -3479,10 +3649,10 @@
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="54"/>
+      <c r="G64" s="71"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>145.1</v>
@@ -3493,10 +3663,10 @@
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="54"/>
+      <c r="G65" s="71"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>7.26</v>
@@ -3507,10 +3677,10 @@
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="64" t="s">
+      <c r="F66" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="65"/>
+      <c r="G66" s="76"/>
       <c r="H66" s="26">
         <f>H65/6</f>
         <v>1.21</v>
@@ -3518,29 +3688,29 @@
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E67" s="61" t="s">
+      <c r="E67" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="72"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
     <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="G68" s="62"/>
-      <c r="H68" s="62"/>
-      <c r="I68" s="62"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
     </row>
     <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="63" t="s">
+      <c r="E69" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="63"/>
+      <c r="F69" s="74"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -3585,19 +3755,19 @@
     <col min="6" max="6" width="52.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="19">
         <v>20</v>
       </c>
@@ -3628,11 +3798,11 @@
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="66" t="str">
+      <c r="F4" s="83" t="str">
         <f>"с 01 сентября по 28 сентября (" &amp; J1 &amp; " рабочих дней)"</f>
         <v>с 01 сентября по 28 сентября (20 рабочих дней)</v>
       </c>
-      <c r="G4" s="66"/>
+      <c r="G4" s="83"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
@@ -3789,19 +3959,19 @@
       </c>
     </row>
     <row r="14" spans="5:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="67">
+      <c r="E14" s="53">
         <v>8</v>
       </c>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="69">
+      <c r="G14" s="55">
         <v>3</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="55">
         <v>16</v>
       </c>
-      <c r="I14" s="70">
+      <c r="I14" s="56">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -3819,19 +3989,19 @@
       <c r="H15" s="51">
         <v>4</v>
       </c>
-      <c r="I15" s="73">
+      <c r="I15" s="59">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="5:10" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="71">
+      <c r="E16" s="57">
         <v>10</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="46"/>
       <c r="H16" s="46"/>
-      <c r="I16" s="72">
+      <c r="I16" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4331,22 +4501,22 @@
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="58"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="80"/>
       <c r="I59" s="6"/>
     </row>
     <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="60"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
@@ -4356,10 +4526,10 @@
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="54"/>
+      <c r="G61" s="71"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>20</v>
@@ -4370,10 +4540,10 @@
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="53" t="s">
+      <c r="F62" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="54"/>
+      <c r="G62" s="71"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>160</v>
@@ -4384,10 +4554,10 @@
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="53" t="s">
+      <c r="F63" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="54"/>
+      <c r="G63" s="71"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>60</v>
@@ -4398,10 +4568,10 @@
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="54"/>
+      <c r="G64" s="71"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>177.55</v>
@@ -4412,10 +4582,10 @@
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="54"/>
+      <c r="G65" s="71"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>8.8800000000000008</v>
@@ -4426,10 +4596,10 @@
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="64" t="s">
+      <c r="F66" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="65"/>
+      <c r="G66" s="76"/>
       <c r="H66" s="26">
         <f>H65/8</f>
         <v>1.1100000000000001</v>
@@ -4437,29 +4607,29 @@
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E67" s="61" t="s">
+      <c r="E67" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="72"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
     <row r="68" spans="5:15" ht="111" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="G68" s="62"/>
-      <c r="H68" s="62"/>
-      <c r="I68" s="62"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
     </row>
     <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="63" t="s">
+      <c r="E69" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="63"/>
+      <c r="F69" s="74"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -4505,19 +4675,19 @@
     <col min="6" max="6" width="52.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="19">
         <v>63</v>
       </c>
@@ -4548,11 +4718,11 @@
       <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="66" t="str">
+      <c r="F4" s="83" t="str">
         <f>"с 01 июля по 28 сентября (" &amp; J1 &amp; " рабочих дня)"</f>
         <v>с 01 июля по 28 сентября (63 рабочих дня)</v>
       </c>
-      <c r="G4" s="66"/>
+      <c r="G4" s="83"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
@@ -4564,19 +4734,19 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="76" t="s">
+      <c r="E6" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="76" t="s">
+      <c r="G6" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="77" t="s">
+      <c r="H6" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="78" t="s">
+      <c r="I6" s="64" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4594,7 +4764,7 @@
       <c r="H7" s="16">
         <v>2.5</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="65">
         <f t="shared" ref="I7:I56" si="0">G7*H7</f>
         <v>175</v>
       </c>
@@ -4613,7 +4783,7 @@
       <c r="H8" s="16">
         <v>2</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="65">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
@@ -4632,7 +4802,7 @@
       <c r="H9" s="16">
         <v>2</v>
       </c>
-      <c r="I9" s="79">
+      <c r="I9" s="65">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -4650,7 +4820,7 @@
       <c r="H10" s="16">
         <v>20</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="65">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -4669,7 +4839,7 @@
       <c r="H11" s="16">
         <v>0.5</v>
       </c>
-      <c r="I11" s="79">
+      <c r="I11" s="65">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
@@ -4687,7 +4857,7 @@
       <c r="H12" s="16">
         <v>30</v>
       </c>
-      <c r="I12" s="79">
+      <c r="I12" s="65">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -4706,7 +4876,7 @@
       <c r="H13" s="16">
         <v>0.35</v>
       </c>
-      <c r="I13" s="79">
+      <c r="I13" s="65">
         <f t="shared" si="0"/>
         <v>11.899999999999999</v>
       </c>
@@ -4724,7 +4894,7 @@
       <c r="H14" s="16">
         <v>20</v>
       </c>
-      <c r="I14" s="79">
+      <c r="I14" s="65">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -4742,7 +4912,7 @@
       <c r="H15" s="16">
         <v>4</v>
       </c>
-      <c r="I15" s="79">
+      <c r="I15" s="65">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -4760,7 +4930,7 @@
       <c r="H16" s="16">
         <v>12</v>
       </c>
-      <c r="I16" s="79">
+      <c r="I16" s="65">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -4778,13 +4948,13 @@
       <c r="H17" s="16">
         <v>1</v>
       </c>
-      <c r="I17" s="79">
+      <c r="I17" s="65">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="5:9" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="80">
+      <c r="E18" s="66">
         <v>12</v>
       </c>
       <c r="F18" s="47" t="s">
@@ -4797,7 +4967,7 @@
       <c r="H18" s="16">
         <v>2.5</v>
       </c>
-      <c r="I18" s="79">
+      <c r="I18" s="65">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -4816,7 +4986,7 @@
       <c r="H19" s="16">
         <v>1</v>
       </c>
-      <c r="I19" s="79">
+      <c r="I19" s="65">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -4834,13 +5004,13 @@
       <c r="H20" s="16">
         <v>2.5</v>
       </c>
-      <c r="I20" s="79">
+      <c r="I20" s="65">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="5:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="E21" s="81">
+      <c r="E21" s="67">
         <v>15</v>
       </c>
       <c r="F21" s="45" t="s">
@@ -4852,7 +5022,7 @@
       <c r="H21" s="46">
         <v>1</v>
       </c>
-      <c r="I21" s="82">
+      <c r="I21" s="68">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -4862,7 +5032,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G22" s="17">
         <v>1</v>
@@ -4880,13 +5050,13 @@
         <v>17</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="83">
+        <v>52</v>
+      </c>
+      <c r="G23" s="69">
         <f>J1/2+0.5</f>
         <v>32</v>
       </c>
-      <c r="H23" s="83">
+      <c r="H23" s="69">
         <v>1.25</v>
       </c>
       <c r="I23" s="41">
@@ -4895,7 +5065,7 @@
       </c>
     </row>
     <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="74">
+      <c r="E24" s="60">
         <v>18</v>
       </c>
       <c r="F24" s="45"/>
@@ -5305,22 +5475,22 @@
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="58"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="80"/>
       <c r="I59" s="6"/>
     </row>
     <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E60" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="60"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="22" t="s">
         <v>17</v>
       </c>
@@ -5330,10 +5500,10 @@
       <c r="E61" s="23">
         <v>1</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="54"/>
+      <c r="G61" s="71"/>
       <c r="H61" s="24">
         <f>J1</f>
         <v>63</v>
@@ -5344,10 +5514,10 @@
       <c r="E62" s="23">
         <v>2</v>
       </c>
-      <c r="F62" s="53" t="s">
+      <c r="F62" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="54"/>
+      <c r="G62" s="71"/>
       <c r="H62" s="24">
         <f>H61*8</f>
         <v>504</v>
@@ -5358,10 +5528,10 @@
       <c r="E63" s="23">
         <v>3</v>
       </c>
-      <c r="F63" s="53" t="s">
+      <c r="F63" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="54"/>
+      <c r="G63" s="71"/>
       <c r="H63" s="24">
         <f>SUM(G7:G56)</f>
         <v>296</v>
@@ -5372,10 +5542,10 @@
       <c r="E64" s="23">
         <v>4</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="54"/>
+      <c r="G64" s="71"/>
       <c r="H64" s="24">
         <f>SUM(I7:I56)</f>
         <v>607.4</v>
@@ -5386,10 +5556,10 @@
       <c r="E65" s="23">
         <v>5</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="54"/>
+      <c r="G65" s="71"/>
       <c r="H65" s="24">
         <f>ROUND(H64/H61,2)</f>
         <v>9.64</v>
@@ -5400,10 +5570,10 @@
       <c r="E66" s="25">
         <v>6</v>
       </c>
-      <c r="F66" s="64" t="s">
+      <c r="F66" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="65"/>
+      <c r="G66" s="76"/>
       <c r="H66" s="26">
         <f>H65/(8-3.2)</f>
         <v>2.0083333333333337</v>
@@ -5411,29 +5581,1073 @@
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E67" s="61" t="s">
+      <c r="E67" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="72"/>
       <c r="G67" s="10"/>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="O67" s="11"/>
     </row>
     <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
+    </row>
+    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="74"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="55" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="4" max="1048575" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E1:O70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="52.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E1" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="G68" s="62"/>
-      <c r="H68" s="62"/>
-      <c r="I68" s="62"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="19">
+        <f>63+117</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="83" t="str">
+        <f>"с 12 января по 28 сентября (" &amp; J1 &amp; " рабочих дней)"</f>
+        <v>с 12 января по 28 сентября (180 рабочих дней)</v>
+      </c>
+      <c r="G4" s="83"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="90" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="90" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="92" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="5:10" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="48">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="16">
+        <f>21+24+25+67</f>
+        <v>137</v>
+      </c>
+      <c r="H7" s="16">
+        <v>3</v>
+      </c>
+      <c r="I7" s="65">
+        <f t="shared" ref="I7:I56" si="0">G7*H7</f>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8" spans="5:10" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="48">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="16">
+        <f>14+23+20</f>
+        <v>57</v>
+      </c>
+      <c r="H8" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="65">
+        <f t="shared" si="0"/>
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="9" spans="5:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="48">
+        <v>3</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="16">
+        <f>3+10+10+71-15</f>
+        <v>79</v>
+      </c>
+      <c r="H9" s="16">
+        <v>2</v>
+      </c>
+      <c r="I9" s="65">
+        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="5:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="48">
+        <v>4</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="16">
+        <v>30</v>
+      </c>
+      <c r="I10" s="65">
+        <f>G10*H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="48">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="16">
+        <v>3</v>
+      </c>
+      <c r="H11" s="16">
+        <v>20</v>
+      </c>
+      <c r="I11" s="65">
+        <f>G11*H11</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="48">
+        <v>6</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="16">
+        <v>20</v>
+      </c>
+      <c r="I12" s="65">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="48">
+        <v>7</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="16">
+        <f>3+12+10+10</f>
+        <v>35</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="65">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="48">
+        <v>8</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="16">
+        <f>15+39</f>
+        <v>54</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1</v>
+      </c>
+      <c r="I14" s="65">
+        <f>G14*H14</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="48">
+        <v>9</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16">
+        <v>12</v>
+      </c>
+      <c r="I15" s="65">
+        <f>G15*H15</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="48">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="86">
+        <v>2</v>
+      </c>
+      <c r="H16" s="86">
+        <v>8</v>
+      </c>
+      <c r="I16" s="65">
+        <f>G16*H16</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="48">
+        <v>11</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="86">
+        <v>20</v>
+      </c>
+      <c r="H17" s="86">
+        <v>4</v>
+      </c>
+      <c r="I17" s="65">
+        <f>G17*H17</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="48">
+        <v>12</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="16">
+        <f>13+21</f>
+        <v>34</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="I18" s="65">
+        <f t="shared" si="0"/>
+        <v>11.899999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="48">
+        <v>13</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="16">
+        <v>4</v>
+      </c>
+      <c r="I19" s="65">
+        <f>G19*H19</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="48">
+        <v>14</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="86">
+        <v>24</v>
+      </c>
+      <c r="H20" s="86">
+        <v>0.45</v>
+      </c>
+      <c r="I20" s="65">
+        <f>G20*H20</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="48">
+        <v>15</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="86">
+        <v>40</v>
+      </c>
+      <c r="H21" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="65">
+        <f>G21*H21</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="48">
+        <v>16</v>
+      </c>
+      <c r="F22" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="86">
+        <v>1</v>
+      </c>
+      <c r="H22" s="86">
+        <f>9*8</f>
+        <v>72</v>
+      </c>
+      <c r="I22" s="65">
+        <f>G22*H22</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="48">
+        <v>17</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="16">
+        <f>3+9+32</f>
+        <v>44</v>
+      </c>
+      <c r="H23" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I23" s="65">
+        <f>G23*H23</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="48">
+        <v>18</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="16">
+        <f>3+9+32</f>
+        <v>44</v>
+      </c>
+      <c r="H24" s="16">
+        <v>1.25</v>
+      </c>
+      <c r="I24" s="65">
+        <f>G24*H24</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="48">
+        <v>19</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="16">
+        <v>8</v>
+      </c>
+      <c r="H25" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I25" s="65">
+        <f>G25*H25</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="5:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="48">
+        <v>20</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="17">
+        <v>20</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1</v>
+      </c>
+      <c r="I26" s="65">
+        <f>G26*H26</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="48">
+        <v>21</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="17">
+        <v>25</v>
+      </c>
+      <c r="I27" s="65">
+        <f>G27*H27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="48">
+        <v>22</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="17">
+        <f>J1/2</f>
+        <v>90</v>
+      </c>
+      <c r="H28" s="17">
+        <v>1.25</v>
+      </c>
+      <c r="I28" s="65">
+        <f>ROUND(G28*H28,2)</f>
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="29" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="48">
+        <v>23</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="86">
+        <f>17*1.2</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="H29" s="86">
+        <v>4</v>
+      </c>
+      <c r="I29" s="65">
+        <f t="shared" si="0"/>
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="48">
+        <v>24</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="86">
+        <v>40</v>
+      </c>
+      <c r="H30" s="86">
+        <v>2</v>
+      </c>
+      <c r="I30" s="65">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="48">
+        <v>25</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="86">
+        <v>18</v>
+      </c>
+      <c r="H31" s="86">
+        <v>2</v>
+      </c>
+      <c r="I31" s="65">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="48">
+        <v>26</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="86">
+        <v>8</v>
+      </c>
+      <c r="H32" s="86">
+        <v>3.5</v>
+      </c>
+      <c r="I32" s="65">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="48">
+        <v>27</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="86">
+        <v>2</v>
+      </c>
+      <c r="H33" s="86">
+        <v>5</v>
+      </c>
+      <c r="I33" s="65">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E34" s="48">
+        <v>28</v>
+      </c>
+      <c r="F34" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="93">
+        <v>1</v>
+      </c>
+      <c r="H34" s="93">
+        <v>19</v>
+      </c>
+      <c r="I34" s="59">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="57">
+        <v>29</v>
+      </c>
+      <c r="F35" s="45"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="84">
+        <v>30</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="84">
+        <v>31</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="87">
+        <v>32</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="84">
+        <v>33</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="84">
+        <v>34</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="84">
+        <v>35</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="84">
+        <v>36</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="84">
+        <v>37</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="84">
+        <v>38</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="87">
+        <v>39</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="84">
+        <v>40</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="84">
+        <v>41</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="84">
+        <v>42</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="84">
+        <v>43</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="84">
+        <v>44</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="84">
+        <v>45</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="87">
+        <v>46</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="84">
+        <v>47</v>
+      </c>
+      <c r="F53" s="12"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="84">
+        <v>48</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="84">
+        <v>49</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="5:9" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E56" s="84">
+        <v>50</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="80"/>
+      <c r="I59" s="6"/>
+    </row>
+    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E60" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F60" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="82"/>
+      <c r="H60" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E61" s="23">
+        <v>1</v>
+      </c>
+      <c r="F61" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="71"/>
+      <c r="H61" s="24">
+        <f>J1</f>
+        <v>180</v>
+      </c>
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E62" s="23">
+        <v>2</v>
+      </c>
+      <c r="F62" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="71"/>
+      <c r="H62" s="24">
+        <f>H61*8</f>
+        <v>1440</v>
+      </c>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E63" s="23">
+        <v>3</v>
+      </c>
+      <c r="F63" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="71"/>
+      <c r="H63" s="24">
+        <f>SUM(G7:G56)</f>
+        <v>786.4</v>
+      </c>
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="23">
+        <v>4</v>
+      </c>
+      <c r="F64" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="71"/>
+      <c r="H64" s="24">
+        <f>SUM(I7:I56)</f>
+        <v>1716.8</v>
+      </c>
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E65" s="23">
+        <v>5</v>
+      </c>
+      <c r="F65" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="71"/>
+      <c r="H65" s="24">
+        <f>ROUND(H64/H61,2)</f>
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E66" s="25">
+        <v>6</v>
+      </c>
+      <c r="F66" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="76"/>
+      <c r="H66" s="26">
+        <f>H65/(8-3.3)</f>
+        <v>2.0297872340425531</v>
+      </c>
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="72"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
     </row>
     <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="63" t="s">
+      <c r="E69" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="63"/>
+      <c r="F69" s="74"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -5467,978 +6681,4 @@
     <brk id="4" max="1048575" man="1"/>
   </colBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E1:O70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="52.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="19">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E4" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="66" t="str">
-        <f>"с 01 июля по 28 сентября (" &amp; J1 &amp; " рабочих дня)"</f>
-        <v>с 01 июля по 28 сентября (63 рабочих дня)</v>
-      </c>
-      <c r="G4" s="66"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="5:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="5:10" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="48">
-        <v>1</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="16">
-        <f>21+24+25</f>
-        <v>70</v>
-      </c>
-      <c r="H7" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="I7" s="79">
-        <f t="shared" ref="I7:I56" si="0">G7*H7</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="5:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="48">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="16">
-        <f>14+23</f>
-        <v>37</v>
-      </c>
-      <c r="H8" s="16">
-        <v>2</v>
-      </c>
-      <c r="I8" s="79">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E9" s="48">
-        <v>3</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="16">
-        <f>3+10+10</f>
-        <v>23</v>
-      </c>
-      <c r="H9" s="16">
-        <v>2</v>
-      </c>
-      <c r="I9" s="79">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="48">
-        <v>4</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="16">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16">
-        <v>20</v>
-      </c>
-      <c r="I10" s="79">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E11" s="48">
-        <v>5</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="16">
-        <f>3+12+10</f>
-        <v>25</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="79">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="12" spans="5:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="48">
-        <v>6</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="16">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16">
-        <v>30</v>
-      </c>
-      <c r="I12" s="79">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="48">
-        <v>7</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="16">
-        <f>13+21</f>
-        <v>34</v>
-      </c>
-      <c r="H13" s="16">
-        <v>0.35</v>
-      </c>
-      <c r="I13" s="79">
-        <f t="shared" si="0"/>
-        <v>11.899999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="48">
-        <v>8</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="16">
-        <v>3</v>
-      </c>
-      <c r="H14" s="16">
-        <v>20</v>
-      </c>
-      <c r="I14" s="79">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E15" s="48">
-        <v>9</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16">
-        <v>4</v>
-      </c>
-      <c r="I15" s="79">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="5:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="48">
-        <v>10</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16">
-        <v>12</v>
-      </c>
-      <c r="I16" s="79">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E17" s="48">
-        <v>8</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="16">
-        <v>15</v>
-      </c>
-      <c r="H17" s="16">
-        <v>1</v>
-      </c>
-      <c r="I17" s="79">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="80">
-        <v>12</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="16">
-        <f>3+9</f>
-        <v>12</v>
-      </c>
-      <c r="H18" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="I18" s="79">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="5:9" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="48">
-        <v>13</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="16">
-        <f>3+9</f>
-        <v>12</v>
-      </c>
-      <c r="H19" s="16">
-        <v>1</v>
-      </c>
-      <c r="I19" s="79">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="5:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="48">
-        <v>14</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="16">
-        <v>8</v>
-      </c>
-      <c r="H20" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="I20" s="79">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="5:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="E21" s="81">
-        <v>15</v>
-      </c>
-      <c r="F21" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="46">
-        <v>20</v>
-      </c>
-      <c r="H21" s="46">
-        <v>1</v>
-      </c>
-      <c r="I21" s="82">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="5:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="E22" s="35">
-        <v>16</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" s="17">
-        <v>1</v>
-      </c>
-      <c r="H22" s="17">
-        <v>25</v>
-      </c>
-      <c r="I22" s="36">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="5:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E23" s="38">
-        <v>17</v>
-      </c>
-      <c r="F23" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="83">
-        <f>J1/2+0.5</f>
-        <v>32</v>
-      </c>
-      <c r="H23" s="83">
-        <v>1.25</v>
-      </c>
-      <c r="I23" s="41">
-        <f>ROUND(G23*H23,2)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="74">
-        <v>18</v>
-      </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="5">
-        <v>19</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="5">
-        <v>20</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E27" s="13">
-        <v>21</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="5">
-        <v>22</v>
-      </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="5">
-        <v>23</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="5">
-        <v>24</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="7">
-        <v>25</v>
-      </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E32" s="5">
-        <v>26</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E33" s="5">
-        <v>27</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E34" s="5">
-        <v>28</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="5">
-        <v>29</v>
-      </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="5">
-        <v>30</v>
-      </c>
-      <c r="F36" s="12"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E37" s="5">
-        <v>31</v>
-      </c>
-      <c r="F37" s="12"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="7">
-        <v>32</v>
-      </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E39" s="5">
-        <v>33</v>
-      </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E40" s="5">
-        <v>34</v>
-      </c>
-      <c r="F40" s="12"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E41" s="5">
-        <v>35</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E42" s="5">
-        <v>36</v>
-      </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E43" s="5">
-        <v>37</v>
-      </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E44" s="5">
-        <v>38</v>
-      </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E45" s="7">
-        <v>39</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E46" s="5">
-        <v>40</v>
-      </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E47" s="5">
-        <v>41</v>
-      </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E48" s="5">
-        <v>42</v>
-      </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E49" s="5">
-        <v>43</v>
-      </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E50" s="5">
-        <v>44</v>
-      </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E51" s="5">
-        <v>45</v>
-      </c>
-      <c r="F51" s="12"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E52" s="7">
-        <v>46</v>
-      </c>
-      <c r="F52" s="12"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E53" s="5">
-        <v>47</v>
-      </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E54" s="5">
-        <v>48</v>
-      </c>
-      <c r="F54" s="12"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E55" s="5">
-        <v>49</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E56" s="5">
-        <v>50</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-    </row>
-    <row r="59" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E59" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="6"/>
-    </row>
-    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E60" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F60" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="60"/>
-      <c r="H60" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I60" s="6"/>
-    </row>
-    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E61" s="23">
-        <v>1</v>
-      </c>
-      <c r="F61" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="54"/>
-      <c r="H61" s="24">
-        <f>J1</f>
-        <v>63</v>
-      </c>
-      <c r="I61" s="6"/>
-    </row>
-    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E62" s="23">
-        <v>2</v>
-      </c>
-      <c r="F62" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="G62" s="54"/>
-      <c r="H62" s="24">
-        <f>H61*8</f>
-        <v>504</v>
-      </c>
-      <c r="I62" s="6"/>
-    </row>
-    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E63" s="23">
-        <v>3</v>
-      </c>
-      <c r="F63" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" s="54"/>
-      <c r="H63" s="24">
-        <f>SUM(G7:G56)</f>
-        <v>296</v>
-      </c>
-      <c r="I63" s="6"/>
-    </row>
-    <row r="64" spans="5:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E64" s="23">
-        <v>4</v>
-      </c>
-      <c r="F64" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="54"/>
-      <c r="H64" s="24">
-        <f>SUM(I7:I56)</f>
-        <v>607.4</v>
-      </c>
-      <c r="I64" s="6"/>
-    </row>
-    <row r="65" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E65" s="23">
-        <v>5</v>
-      </c>
-      <c r="F65" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65" s="54"/>
-      <c r="H65" s="24">
-        <f>ROUND(H64/H61,2)</f>
-        <v>9.64</v>
-      </c>
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" spans="5:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E66" s="25">
-        <v>6</v>
-      </c>
-      <c r="F66" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="65"/>
-      <c r="H66" s="26">
-        <f>H65/(8-3.2)</f>
-        <v>2.0083333333333337</v>
-      </c>
-      <c r="I66" s="6"/>
-    </row>
-    <row r="67" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E67" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="F67" s="61"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="O67" s="11"/>
-    </row>
-    <row r="68" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="F68" s="62"/>
-      <c r="G68" s="62"/>
-      <c r="H68" s="62"/>
-      <c r="I68" s="62"/>
-    </row>
-    <row r="69" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="63"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-    </row>
-    <row r="70" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-  </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="55" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="4" max="1048575" man="1"/>
-  </colBreaks>
-</worksheet>
 </file>